--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97209</v>
+        <v>97210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103762</v>
+        <v>103763</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B11" t="n">
-        <v>98235</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,39 +1645,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R11" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B12" t="n">
-        <v>98333</v>
+        <v>98236</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,41 +1752,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R12" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105340</v>
+        <v>105341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125974001</v>
+        <v>125974103</v>
       </c>
       <c r="B4" t="n">
-        <v>98238</v>
+        <v>103765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -905,17 +905,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -960,11 +952,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125974103</v>
+        <v>125974001</v>
       </c>
       <c r="B5" t="n">
-        <v>103763</v>
+        <v>98240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,16 +990,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1020,9 +1007,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,41 +1645,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R11" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,22 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98236</v>
+        <v>98336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,39 +1745,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R12" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,6 +1809,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105341</v>
+        <v>105343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125974103</v>
+        <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>103765</v>
+        <v>98244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -905,9 +905,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -952,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125974001</v>
+        <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>103769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,16 +1003,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1007,17 +1020,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98336</v>
+        <v>98340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98238</v>
+        <v>98242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98336</v>
+        <v>98340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105343</v>
+        <v>105347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98340</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98242</v>
+        <v>98243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98340</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105347</v>
+        <v>105348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105348</v>
+        <v>105350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99354</v>
+        <v>99356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B11" t="n">
-        <v>98245</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,39 +1645,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R11" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,41 +1752,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R12" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105350</v>
+        <v>105352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98247</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,41 +1645,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R11" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,22 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98247</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,39 +1745,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R12" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,6 +1809,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99356</v>
+        <v>99358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B11" t="n">
-        <v>98247</v>
+        <v>98347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,39 +1645,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R11" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,41 +1752,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R12" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105352</v>
+        <v>105356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,41 +1645,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R11" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,22 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98249</v>
+        <v>98347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,39 +1745,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R12" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,6 +1809,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99358</v>
+        <v>99362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98351</v>
+        <v>98354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98351</v>
+        <v>98354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125974001</v>
+        <v>125974103</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>103794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -905,17 +905,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -960,11 +952,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125974103</v>
+        <v>125974001</v>
       </c>
       <c r="B5" t="n">
-        <v>103794</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,16 +990,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1020,9 +1007,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B11" t="n">
-        <v>98256</v>
+        <v>98354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,39 +1645,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R11" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B12" t="n">
-        <v>98354</v>
+        <v>98256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,41 +1752,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R12" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98354</v>
+        <v>98256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,41 +1645,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R11" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,22 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>98354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,39 +1745,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R12" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1814,6 +1809,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125963309</v>
       </c>
       <c r="B2" t="n">
-        <v>99365</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125974154</v>
       </c>
       <c r="B3" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125974103</v>
       </c>
       <c r="B4" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125974001</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>125963405</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>125974151</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>125963515</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>125963690</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>125963664</v>
       </c>
       <c r="B10" t="n">
-        <v>98354</v>
+        <v>98363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>125963329</v>
       </c>
       <c r="B11" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>125974173</v>
       </c>
       <c r="B12" t="n">
-        <v>98354</v>
+        <v>98363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125974112</v>
       </c>
       <c r="B13" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 55094-2023 artfynd.xlsx
+++ b/artfynd/A 55094-2023 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125974103</v>
+        <v>125974001</v>
       </c>
       <c r="B4" t="n">
-        <v>103803</v>
+        <v>98267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -905,9 +905,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -952,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125974001</v>
+        <v>125974103</v>
       </c>
       <c r="B5" t="n">
-        <v>98267</v>
+        <v>103803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,16 +1003,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1007,17 +1020,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på vägens östra sida. Utmarkerat med snitslar. Torr växtplats exponerat för sol pga hygge. Extremt korta stjälkar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125963329</v>
+        <v>125974173</v>
       </c>
       <c r="B11" t="n">
-        <v>98265</v>
+        <v>98363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,39 +1645,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
+          <t>Gungarebacken vägkant, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673922</v>
+        <v>673914</v>
       </c>
       <c r="R11" t="n">
-        <v>7158105</v>
+        <v>7158111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,22 +1729,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell</t>
+          <t>Katarina Stenman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
+          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125974173</v>
+        <v>125963329</v>
       </c>
       <c r="B12" t="n">
-        <v>98363</v>
+        <v>98265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,41 +1752,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gungarebacken vägkant, Ly lm</t>
+          <t>Tjäderåsen, Tjäderåsen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>673914</v>
+        <v>673922</v>
       </c>
       <c r="R12" t="n">
-        <v>7158111</v>
+        <v>7158105</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>västra sidan vägen i granskogsmyr</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,12 +1829,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katarina Stenman</t>
+          <t>Hans Gardfjell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katarina Stenman, Mats Johansson, Hans Gardfjell, Sven Hellqvist</t>
+          <t>Hans Gardfjell, Katarina Stenman, Sven Hellqvist, Mats Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
